--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -2169,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2186,11 +2186,11 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
@@ -2317,152 +2317,377 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd</t>
+          <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.54654941693749</v>
+        <v>13.0380853616381</v>
       </c>
       <c r="D2" t="n">
-        <v>11.96258436964212</v>
+        <v>5.746523336036321</v>
       </c>
       <c r="E2" t="n">
-        <v>3.060025128683176</v>
+        <v>24.0645524488647</v>
       </c>
       <c r="F2" t="n">
-        <v>9.445547764763102</v>
+        <v>99.50459748545694</v>
       </c>
       <c r="G2" t="n">
-        <v>5.585052486523731</v>
+        <v>99.47082004128355</v>
       </c>
       <c r="H2" t="n">
-        <v>3.58763572429851</v>
+        <v>1.321838369595244</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7616899254444657</v>
+        <v>8.378352548852153</v>
       </c>
       <c r="J2" t="n">
-        <v>5.224737713970182</v>
+        <v>1.31948659270683</v>
       </c>
       <c r="K2" t="n">
-        <v>1.437567045698348</v>
+        <v>15.53898087730547</v>
       </c>
       <c r="L2" t="n">
-        <v>925</v>
+        <v>7906</v>
       </c>
       <c r="M2" t="n">
-        <v>9.922763355503111</v>
+        <v>29.81933391166598</v>
       </c>
       <c r="N2" t="n">
-        <v>7569</v>
+        <v>7914</v>
       </c>
       <c r="O2" t="n">
-        <v>9.211957132942761</v>
+        <v>19.06740855567788</v>
       </c>
       <c r="P2" t="n">
-        <v>7.557399109099472</v>
+        <v>23.24502393394037</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.922384104881218</v>
+        <v>20.11244339814313</v>
       </c>
       <c r="R2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="S2" t="n">
-        <v>1.172420347359167</v>
+        <v>0.05492885738906</v>
       </c>
       <c r="T2" t="n">
-        <v>3.276409268972844</v>
+        <v>1211.136363636364</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>9.539999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>2.38</v>
+        <v>3.91</v>
       </c>
       <c r="W2" t="n">
-        <v>35.36</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bank of Baroda</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15.7618637908999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.712278690337432</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15.93948250956673</v>
+      </c>
+      <c r="F3" t="n">
+        <v>37.4889127294537</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36.05115772223114</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.140275868320467</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.14371872728943</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.896747724261721</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.58378963023052</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-7559</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-17.03283084341693</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-6274</v>
+      </c>
+      <c r="O3" t="n">
+        <v>17.47729766589094</v>
+      </c>
+      <c r="P3" t="n">
+        <v>74.50588066551305</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>55.18455739153598</v>
+      </c>
+      <c r="R3" t="n">
+        <v>21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.07153782236255685</v>
+      </c>
+      <c r="T3" t="n">
+        <v>13.0747735807378</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson International Ltd</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11.54654941693749</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.96258436964212</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.060025128683176</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.445547764763102</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.585052486523731</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.58763572429851</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7616899254444657</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.224737713970182</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.437567045698348</v>
+      </c>
+      <c r="L4" t="n">
+        <v>925</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9.922763355503111</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7569</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9.211957132942761</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7.557399109099472</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.922384104881218</v>
+      </c>
+      <c r="R4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.172420347359167</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.276409268972844</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W4" t="n">
+        <v>35.36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
 </t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>18.53754343556428</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>11.53531575124259</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" t="n">
         <v>8.822387437265419</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>17.89787025985418</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G5" t="n">
         <v>14.50121514545794</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H5" t="n">
         <v>5.227460570376871</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I5" t="n">
         <v>1.641441305333132</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J5" t="n">
         <v>3.764690170940171</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K5" t="n">
         <v>2.950305318977985</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L5" t="n">
         <v>-11245</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M5" t="n">
         <v>-45.17515667684396</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N5" t="n">
         <v>-5630</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O5" t="n">
         <v>5.838805854237616</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P5" t="n">
         <v>15.31688706104797</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q5" t="n">
         <v>16.17550991430385</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R5" t="n">
         <v>21</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S5" t="n">
         <v>0.5925222177725139</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T5" t="n">
         <v>4.944292367307761</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>14.22</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W5" t="n">
         <v>28.29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IndusInd Bank Ltd</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14.25227319776422</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.475962286021232</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.56369677362945</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38.55469091544986</v>
+      </c>
+      <c r="G6" t="n">
+        <v>37.62568855469092</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.738083447425403</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.885742949503957</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.879527055815935</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18.47584760176891</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-17468</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-99.03617190157614</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-16843</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15.49561308335803</v>
+      </c>
+      <c r="P6" t="n">
+        <v>22.07746495394836</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15.89562187541786</v>
+      </c>
+      <c r="R6" t="n">
+        <v>14</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.08884228106460039</v>
+      </c>
+      <c r="T6" t="n">
+        <v>22.86256871564218</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24.28</v>
       </c>
     </row>
   </sheetData>
@@ -5572,7 +5797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5581,7 +5806,7 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -5590,8 +5815,8 @@
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
     <col width="27" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
@@ -5795,4283 +6020,1354 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nestle India Ltd</t>
+          <t>Trent Ltd</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117.7544910179641</v>
+        <v>36.30776794493609</v>
       </c>
       <c r="D3" t="n">
-        <v>143.1478968792402</v>
+        <v>22.33293248582718</v>
       </c>
       <c r="E3" t="n">
-        <v>16.12281708616873</v>
+        <v>11.93535353535353</v>
       </c>
       <c r="F3" t="n">
-        <v>23.82963023694351</v>
+        <v>15.92727272727273</v>
       </c>
       <c r="G3" t="n">
-        <v>21.62416987783881</v>
+        <v>10.50505050505051</v>
       </c>
       <c r="H3" t="n">
-        <v>37.37527321106148</v>
+        <v>20.62273108070371</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1032934131736527</v>
+        <v>0.4309242871189774</v>
       </c>
       <c r="J3" t="n">
-        <v>41.18620689655172</v>
+        <v>8.043478260869565</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.02047135730259763</v>
+        <v>0.1709791983764586</v>
       </c>
       <c r="L3" t="n">
-        <v>2938</v>
+        <v>841</v>
       </c>
       <c r="M3" t="n">
-        <v>50.54188886977465</v>
+        <v>42.66869609335362</v>
       </c>
       <c r="N3" t="n">
-        <v>4175</v>
+        <v>1349</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>14.54857371180267</v>
+        <v>36.30691600183056</v>
       </c>
       <c r="P3" t="n">
-        <v>14.85231951299384</v>
+        <v>73.11367578503176</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.43852585822143</v>
+        <v>69.52182030724354</v>
       </c>
       <c r="R3" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>2.318160220469448</v>
+        <v>1.727869310248534</v>
       </c>
       <c r="T3" t="n">
-        <v>7.050289017341041</v>
+        <v>5.051020408163265</v>
       </c>
       <c r="U3" t="n">
-        <v>54.96</v>
+        <v>8.65</v>
       </c>
       <c r="V3" t="n">
-        <v>14.34</v>
+        <v>11.82</v>
       </c>
       <c r="W3" t="n">
-        <v>72.01000000000001</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adani Power Ltd</t>
+          <t>Bajaj Holdings &amp; Investment Ltd</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48.27674122146251</v>
+        <v>13.57678765646027</v>
       </c>
       <c r="D4" t="n">
-        <v>18.38582322758195</v>
+        <v>2.813478180813846</v>
       </c>
       <c r="E4" t="n">
-        <v>41.36759945184802</v>
+        <v>432.7262044653349</v>
       </c>
       <c r="F4" t="n">
-        <v>36.20186292228556</v>
+        <v>91.77438307873091</v>
       </c>
       <c r="G4" t="n">
-        <v>28.39466942066692</v>
+        <v>89.77673325499413</v>
       </c>
       <c r="H4" t="n">
-        <v>22.63800280407352</v>
+        <v>11.30277313116742</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8023177656738903</v>
+        <v>0.001161354544951794</v>
       </c>
       <c r="J4" t="n">
-        <v>8.297225501770956</v>
+        <v>3764.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.878538512179065</v>
+        <v>-41.39052496798976</v>
       </c>
       <c r="L4" t="n">
-        <v>17651</v>
+        <v>1469</v>
       </c>
       <c r="M4" t="n">
-        <v>96.83454026771999</v>
+        <v>94.04609475032009</v>
       </c>
       <c r="N4" t="n">
-        <v>14170</v>
+        <v>1941</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>16.08609641044097</v>
+        <v>31.61229344896917</v>
       </c>
       <c r="P4" t="n">
-        <v/>
+        <v>19.2975590637313</v>
       </c>
       <c r="Q4" t="n">
-        <v/>
+        <v>18.96864732798973</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5472399439185297</v>
+        <v>0.02611991835607188</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7990192966865558</v>
+        <v>6.975409836065574</v>
       </c>
       <c r="U4" t="n">
-        <v>44.57</v>
+        <v>37.73</v>
       </c>
       <c r="V4" t="n">
-        <v>9.91</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>71.56999999999999</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
+</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.39628482972136</v>
+        <v>15.3548827162833</v>
       </c>
       <c r="D5" t="n">
-        <v>42.82674772036474</v>
+        <v>11.44374462092168</v>
       </c>
       <c r="E5" t="n">
-        <v>26.01873536299766</v>
+        <v>30.33956048070083</v>
       </c>
       <c r="F5" t="n">
-        <v>34.33255269320843</v>
+        <v>58.36172363445772</v>
       </c>
       <c r="G5" t="n">
-        <v>32.99765807962529</v>
+        <v>43.80592265358841</v>
       </c>
       <c r="H5" t="n">
-        <v>18.24002626826465</v>
+        <v>6.926554927819896</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01857585139318885</v>
+        <v>0.9373223691689719</v>
       </c>
       <c r="J5" t="n">
-        <v>82.73684210526316</v>
+        <v>5.949506037321624</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04092769440654843</v>
+        <v>2.898261594714222</v>
       </c>
       <c r="L5" t="n">
-        <v>667</v>
+        <v>8250</v>
       </c>
       <c r="M5" t="n">
-        <v>45.49795361527968</v>
+        <v>52.92193213163128</v>
       </c>
       <c r="N5" t="n">
-        <v>882</v>
+        <v>15018</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>17.95524410389091</v>
+        <v>19.57867595245697</v>
       </c>
       <c r="P5" t="n">
-        <v>29.16686408659448</v>
+        <v>14.90956518204163</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.47351571234393</v>
+        <v>14.86983549970351</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7010343129207027</v>
+        <v>0.2283010965905692</v>
       </c>
       <c r="T5" t="n">
-        <v>12.44897959183673</v>
+        <v>0.3554452546973971</v>
       </c>
       <c r="U5" t="n">
-        <v>60.44</v>
+        <v>48.9</v>
       </c>
       <c r="V5" t="n">
-        <v>5.74</v>
+        <v>2.31</v>
       </c>
       <c r="W5" t="n">
-        <v>71.06</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd</t>
+          <t>LTIMindtree Ltd</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.94431367348518</v>
+        <v>22.9043860525527</v>
       </c>
       <c r="D6" t="n">
-        <v>60.2081007004365</v>
+        <v>25.2071166644031</v>
       </c>
       <c r="E6" t="n">
-        <v>19.13671215020777</v>
+        <v>12.90931103415266</v>
       </c>
       <c r="F6" t="n">
-        <v>26.69068839692312</v>
+        <v>17.98293774812062</v>
       </c>
       <c r="G6" t="n">
-        <v>24.62130489470429</v>
+        <v>15.67699974660022</v>
       </c>
       <c r="H6" t="n">
-        <v>31.68925978882534</v>
+        <v>16.64609352309033</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0886406082507266</v>
+        <v>0.1034568888000799</v>
       </c>
       <c r="J6" t="n">
-        <v>87.09511568123393</v>
+        <v>31.93243243243243</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3692453651860147</v>
+        <v>-1.044778456239236</v>
       </c>
       <c r="L6" t="n">
-        <v>50429</v>
+        <v>1752</v>
       </c>
       <c r="M6" t="n">
-        <v>78.43256190120692</v>
+        <v>27.43071864725223</v>
       </c>
       <c r="N6" t="n">
-        <v>44338</v>
+        <v>5670</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>10.4636148017166</v>
+        <v>30.32798083513346</v>
       </c>
       <c r="P6" t="n">
-        <v>7.871172131953608</v>
+        <v>24.775129058601</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.618771612987096</v>
+        <v>12.24383304425547</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
-        <v>1.655940662120545</v>
+        <v>1.289464130119082</v>
       </c>
       <c r="T6" t="n">
-        <v>12.28795143848194</v>
+        <v>7.13049588436057</v>
       </c>
       <c r="U6" t="n">
-        <v>78.69</v>
+        <v>64.52</v>
       </c>
       <c r="V6" t="n">
-        <v>6.08</v>
+        <v>2.38</v>
       </c>
       <c r="W6" t="n">
-        <v>68.88</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd</t>
+          <t>HDFC Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4744.047619047619</v>
+        <v>10.73230601390972</v>
       </c>
       <c r="D7" t="n">
-        <v>3628.346456692913</v>
+        <v>645.952868852459</v>
       </c>
       <c r="E7" t="n">
-        <v>19.66153542530096</v>
+        <v>1.551013972921306</v>
       </c>
       <c r="F7" t="n">
-        <v>24.92105782514308</v>
+        <v>99.47675449833469</v>
       </c>
       <c r="G7" t="n">
-        <v>22.73534635879219</v>
+        <v>99.39890818076113</v>
       </c>
       <c r="H7" t="n">
-        <v>2475.155279503106</v>
+        <v>0.5200091183301563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.06477567162143734</v>
       </c>
       <c r="J7" t="n">
-        <v>476.75</v>
+        <v>192.2895238095238</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008315185111859039</v>
+        <v>-2.874444037206169</v>
       </c>
       <c r="L7" t="n">
-        <v>-1265</v>
+        <v>-2893</v>
       </c>
       <c r="M7" t="n">
-        <v>-25.04454563452781</v>
+        <v>-2.865746748422502</v>
       </c>
       <c r="N7" t="n">
-        <v>4659</v>
+        <v>10721</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>10.7508063318833</v>
+        <v>21.16813430936688</v>
       </c>
       <c r="P7" t="n">
-        <v>16.12648618019128</v>
+        <v>4.25449161597129</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.75663432482901</v>
+        <v>3.131030647754507</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="S7" t="n">
-        <v>125.888198757764</v>
+        <v>0.3352704278677314</v>
       </c>
       <c r="T7" t="n">
-        <v>1126</v>
+        <v>65.51452550032279</v>
       </c>
       <c r="U7" t="n">
-        <v>17.89</v>
+        <v>50.59</v>
       </c>
       <c r="V7" t="n">
-        <v>9.220000000000001</v>
+        <v>11.28</v>
       </c>
       <c r="W7" t="n">
-        <v>68.41</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd</t>
+          <t xml:space="preserve">Titan Company Ltd
+</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77.66510140873214</v>
+        <v>37.2192057915469</v>
       </c>
       <c r="D8" t="n">
-        <v>118.5341120014487</v>
+        <v>18.8916977649372</v>
       </c>
       <c r="E8" t="n">
-        <v>7.031246466738726</v>
+        <v>6.843630099444054</v>
       </c>
       <c r="F8" t="n">
-        <v>13.50666853599743</v>
+        <v>10.35940803382664</v>
       </c>
       <c r="G8" t="n">
-        <v>11.8414566307725</v>
+        <v>9.21619293712317</v>
       </c>
       <c r="H8" t="n">
-        <v>56.44423467905896</v>
+        <v>11.08187783307446</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1034568888000799</v>
+        <v>1.653145959757266</v>
       </c>
       <c r="J8" t="n">
-        <v>3.544154751892346</v>
+        <v>9.411954765751211</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2234388079691947</v>
+        <v>2.491118669690098</v>
       </c>
       <c r="L8" t="n">
-        <v>20445</v>
+        <v>1506</v>
       </c>
       <c r="M8" t="n">
-        <v>68.45806127574083</v>
+        <v>28.45804988662132</v>
       </c>
       <c r="N8" t="n">
-        <v>18266</v>
+        <v>1695</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>10.33534798968241</v>
+        <v>20.89716395312024</v>
       </c>
       <c r="P8" t="n">
-        <v>8.75885858017449</v>
+        <v>20.27457629679304</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.561693929531589</v>
+        <v>19.50578386760935</v>
       </c>
       <c r="R8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S8" t="n">
-        <v>8.027628521638107</v>
+        <v>1.619298190002219</v>
       </c>
       <c r="T8" t="n">
-        <v>44.39128689018269</v>
+        <v>13.77298463197627</v>
       </c>
       <c r="U8" t="n">
-        <v>30.8</v>
+        <v>10.13</v>
       </c>
       <c r="V8" t="n">
-        <v>2.48</v>
+        <v>10.51</v>
       </c>
       <c r="W8" t="n">
-        <v>66.69</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trent Ltd</t>
+          <t>Adani Total Gas Ltd</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36.30776794493609</v>
+        <v>18.65921787709497</v>
       </c>
       <c r="D9" t="n">
-        <v>22.33293248582718</v>
+        <v>18.41541755888651</v>
       </c>
       <c r="E9" t="n">
-        <v>11.93535353535353</v>
+        <v>14.92737430167598</v>
       </c>
       <c r="F9" t="n">
-        <v>15.92727272727273</v>
+        <v>24.67039106145252</v>
       </c>
       <c r="G9" t="n">
-        <v>10.50505050505051</v>
+        <v>21.13966480446927</v>
       </c>
       <c r="H9" t="n">
-        <v>20.62273108070371</v>
+        <v>10.13349514563107</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4309242871189774</v>
+        <v>0.4349162011173184</v>
       </c>
       <c r="J9" t="n">
-        <v>8.043478260869565</v>
+        <v>10.5045045045045</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1709791983764586</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="L9" t="n">
-        <v>841</v>
+        <v/>
       </c>
       <c r="M9" t="n">
-        <v>42.66869609335362</v>
+        <v/>
       </c>
       <c r="N9" t="n">
-        <v>1349</v>
+        <v/>
       </c>
       <c r="O9" s="2" t="n">
-        <v>36.30691600183056</v>
+        <v>21.08864867789759</v>
       </c>
       <c r="P9" t="n">
-        <v>73.11367578503176</v>
+        <v>23.8762916927858</v>
       </c>
       <c r="Q9" t="n">
-        <v>69.52182030724354</v>
+        <v>24.57309396155174</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.727869310248534</v>
+        <v>0.6788531553398058</v>
       </c>
       <c r="T9" t="n">
-        <v>5.051020408163265</v>
+        <v>1.409892879647133</v>
       </c>
       <c r="U9" t="n">
-        <v>8.65</v>
+        <v>56.96</v>
       </c>
       <c r="V9" t="n">
-        <v>11.82</v>
+        <v>5.76</v>
       </c>
       <c r="W9" t="n">
-        <v>66.47</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd</t>
+          <t>Avenue Supermarts Ltd</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.57678765646027</v>
+        <v>13.56294790886726</v>
       </c>
       <c r="D10" t="n">
-        <v>2.813478180813846</v>
+        <v>17.49611197511664</v>
       </c>
       <c r="E10" t="n">
-        <v>432.7262044653349</v>
+        <v>4.993207190533383</v>
       </c>
       <c r="F10" t="n">
-        <v>91.77438307873091</v>
+        <v>8.084427730414067</v>
       </c>
       <c r="G10" t="n">
-        <v>89.77673325499413</v>
+        <v>6.645139695603379</v>
       </c>
       <c r="H10" t="n">
-        <v>11.30277313116742</v>
+        <v>11.97808426223314</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001161354544951794</v>
+        <v>0.03166114022890149</v>
       </c>
       <c r="J10" t="n">
-        <v>3764.5</v>
+        <v>73.29310344827586</v>
       </c>
       <c r="K10" t="n">
-        <v>-41.39052496798976</v>
+        <v>0.1181198246468583</v>
       </c>
       <c r="L10" t="n">
-        <v>1469</v>
+        <v>278</v>
       </c>
       <c r="M10" t="n">
-        <v>94.04609475032009</v>
+        <v>6.770579639551875</v>
       </c>
       <c r="N10" t="n">
-        <v>1941</v>
+        <v>2746</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>31.61229344896917</v>
+        <v>20.48312440202782</v>
       </c>
       <c r="P10" t="n">
-        <v>19.2975590637313</v>
+        <v>22.96698996520703</v>
       </c>
       <c r="Q10" t="n">
-        <v>18.96864732798973</v>
+        <v>22.74033782145131</v>
       </c>
       <c r="R10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02611991835607188</v>
+        <v>2.398875873795579</v>
       </c>
       <c r="T10" t="n">
-        <v>6.975409836065574</v>
+        <v>3.785985836749907</v>
       </c>
       <c r="U10" t="n">
-        <v>37.73</v>
+        <v>72.53</v>
       </c>
       <c r="V10" t="n">
-        <v>9.380000000000001</v>
+        <v>11.71</v>
       </c>
       <c r="W10" t="n">
-        <v>64.56</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Infosys Ltd</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.78800671841663</v>
+        <v>16.71605179468811</v>
       </c>
       <c r="D11" t="n">
-        <v>32.90697071780254</v>
+        <v>3.09484900948278</v>
       </c>
       <c r="E11" t="n">
-        <v>17.08075746730006</v>
+        <v>13.93516047014541</v>
       </c>
       <c r="F11" t="n">
-        <v>23.70339038198738</v>
+        <v>41.75390656810141</v>
       </c>
       <c r="G11" t="n">
-        <v>20.65920478948396</v>
+        <v>40.93775730869805</v>
       </c>
       <c r="H11" t="n">
-        <v>19.29716218203205</v>
+        <v>1.003310710363005</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09486358890553362</v>
+        <v>14.86741992554242</v>
       </c>
       <c r="J11" t="n">
-        <v>87.52340425531915</v>
+        <v>1.610661174334986</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.446506520247083</v>
+        <v>21.03265721839379</v>
       </c>
       <c r="L11" t="n">
-        <v>20117</v>
+        <v>13296</v>
       </c>
       <c r="M11" t="n">
-        <v>55.22855181880576</v>
+        <v>28.81289819269276</v>
       </c>
       <c r="N11" t="n">
-        <v>25210</v>
+        <v>15046</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>13.19910093055623</v>
+        <v>18.17561078322378</v>
       </c>
       <c r="P11" t="n">
-        <v>11.23941998365794</v>
+        <v>85.7752850068174</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.47461131420948</v>
+        <v>53.4206382524911</v>
       </c>
       <c r="R11" t="n">
-        <v/>
+        <v>19</v>
       </c>
       <c r="S11" t="n">
-        <v>1.129760329363329</v>
+        <v>0.0719985042520674</v>
       </c>
       <c r="T11" t="n">
-        <v>5.563319093476214</v>
+        <v>8.96269564512205</v>
       </c>
       <c r="U11" t="n">
-        <v>35.99</v>
+        <v>36.74</v>
       </c>
       <c r="V11" t="n">
-        <v>8.970000000000001</v>
+        <v>12.61</v>
       </c>
       <c r="W11" t="n">
-        <v>60.02</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
-</t>
+          <t>HDFC Bank Ltd</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.3548827162833</v>
+        <v>14.33974005030719</v>
       </c>
       <c r="D12" t="n">
-        <v>11.44374462092168</v>
+        <v>4.801033923800871</v>
       </c>
       <c r="E12" t="n">
-        <v>30.33956048070083</v>
+        <v>23.07288232992184</v>
       </c>
       <c r="F12" t="n">
-        <v>58.36172363445772</v>
+        <v>61.41252040373843</v>
       </c>
       <c r="G12" t="n">
-        <v>43.80592265358841</v>
+        <v>60.32244076305575</v>
       </c>
       <c r="H12" t="n">
-        <v>6.926554927819896</v>
+        <v>1.623892050854127</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9373223691689719</v>
+        <v>6.808786667718385</v>
       </c>
       <c r="J12" t="n">
-        <v>5.949506037321624</v>
+        <v>1.400768822479211</v>
       </c>
       <c r="K12" t="n">
-        <v>2.898261594714222</v>
+        <v>12.06583962892374</v>
       </c>
       <c r="L12" t="n">
-        <v>8250</v>
+        <v>35669</v>
       </c>
       <c r="M12" t="n">
-        <v>52.92193213163128</v>
+        <v>20.47635996234127</v>
       </c>
       <c r="N12" t="n">
-        <v>15018</v>
+        <v>19069</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>19.57867595245697</v>
+        <v>21.95098428169122</v>
       </c>
       <c r="P12" t="n">
-        <v>14.90956518204163</v>
+        <v>23.86506357287907</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.86983549970351</v>
+        <v>15.42478808253083</v>
       </c>
       <c r="R12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2283010965905692</v>
+        <v>0.07038097917866981</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3554452546973971</v>
+        <v>22.50468105363377</v>
       </c>
       <c r="U12" t="n">
-        <v>48.9</v>
+        <v>49.42</v>
       </c>
       <c r="V12" t="n">
-        <v>2.31</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
-        <v>59.06</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9043860525527</v>
+        <v>13.0380853616381</v>
       </c>
       <c r="D13" t="n">
-        <v>25.2071166644031</v>
+        <v>5.746523336036321</v>
       </c>
       <c r="E13" t="n">
-        <v>12.90931103415266</v>
+        <v>24.0645524488647</v>
       </c>
       <c r="F13" t="n">
-        <v>17.98293774812062</v>
+        <v>99.50459748545694</v>
       </c>
       <c r="G13" t="n">
-        <v>15.67699974660022</v>
+        <v>99.47082004128355</v>
       </c>
       <c r="H13" t="n">
-        <v>16.64609352309033</v>
+        <v>1.321838369595244</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1034568888000799</v>
+        <v>8.378352548852153</v>
       </c>
       <c r="J13" t="n">
-        <v>31.93243243243243</v>
+        <v>1.31948659270683</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.044778456239236</v>
+        <v>15.53898087730547</v>
       </c>
       <c r="L13" t="n">
-        <v>1752</v>
+        <v>7906</v>
       </c>
       <c r="M13" t="n">
-        <v>27.43071864725223</v>
+        <v>29.81933391166598</v>
       </c>
       <c r="N13" t="n">
-        <v>5670</v>
+        <v>7914</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>30.32798083513346</v>
+        <v>19.06740855567788</v>
       </c>
       <c r="P13" t="n">
-        <v>24.775129058601</v>
+        <v>23.24502393394037</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.24383304425547</v>
+        <v>20.11244339814313</v>
       </c>
       <c r="R13" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="S13" t="n">
-        <v>1.289464130119082</v>
+        <v>0.05492885738906</v>
       </c>
       <c r="T13" t="n">
-        <v>7.13049588436057</v>
+        <v>1211.136363636364</v>
       </c>
       <c r="U13" t="n">
-        <v>64.52</v>
+        <v>9.81</v>
       </c>
       <c r="V13" t="n">
-        <v>2.38</v>
+        <v>3.91</v>
       </c>
       <c r="W13" t="n">
-        <v>58.66</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Asian Paints
-Indian Multi-National Paint and Coating Manufacturing Company</t>
+          <t>Adani Enterprises Ltd</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.67748825288338</v>
+        <v>8.534650424813185</v>
       </c>
       <c r="D14" t="n">
-        <v>31.75172153570418</v>
+        <v>7.984787232004292</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6585434568249</v>
+        <v>3.458790097592848</v>
       </c>
       <c r="F14" t="n">
-        <v>21.3692069305536</v>
+        <v>11.79929683367731</v>
       </c>
       <c r="G14" t="n">
-        <v>18.96605155655726</v>
+        <v>8.644382447807013</v>
       </c>
       <c r="H14" t="n">
-        <v>18.58800709006388</v>
+        <v>2.076768834144944</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1321016659547202</v>
+        <v>1.671358378544375</v>
       </c>
       <c r="J14" t="n">
-        <v>41.00487804878049</v>
+        <v>2.749286498353458</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2787079762689519</v>
+        <v>4.975740529137734</v>
       </c>
       <c r="L14" t="n">
-        <v>3556</v>
+        <v>-8455</v>
       </c>
       <c r="M14" t="n">
-        <v>46.88200395517469</v>
+        <v>-74.31660367407929</v>
       </c>
       <c r="N14" t="n">
-        <v>6104</v>
+        <v>10312</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>13.02966034945308</v>
+        <v>19.01541475308124</v>
       </c>
       <c r="P14" t="n">
-        <v>20.27736210195506</v>
+        <v>45.81058899665285</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.97355268843126</v>
+        <v>31.95079107728942</v>
       </c>
       <c r="R14" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.187084044011906</v>
+        <v>0.6004321671876751</v>
       </c>
       <c r="T14" t="n">
-        <v>4.966419476703512</v>
+        <v>1.461411379550759</v>
       </c>
       <c r="U14" t="n">
-        <v>73.37</v>
+        <v>58.87</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9</v>
+        <v>10.41</v>
       </c>
       <c r="W14" t="n">
-        <v>57.79</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd</t>
+          <t>SBI Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.73230601390972</v>
+        <v>12.70458814059566</v>
       </c>
       <c r="D15" t="n">
-        <v>645.952868852459</v>
+        <v>1.140327341024953</v>
       </c>
       <c r="E15" t="n">
-        <v>1.551013972921306</v>
+        <v>1.434978937479165</v>
       </c>
       <c r="F15" t="n">
-        <v>99.47675449833469</v>
+        <v>0.1863805800527321</v>
       </c>
       <c r="G15" t="n">
-        <v>99.39890818076113</v>
+        <v>0.1287995878413189</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5200091183301563</v>
+        <v>0.4755221579767963</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06477567162143734</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>192.2895238095238</v>
+        <v>240.3333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.874444037206169</v>
+        <v>-1564.808943089431</v>
       </c>
       <c r="L15" t="n">
-        <v>-2893</v>
+        <v>-2099</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.865746748422502</v>
+        <v>-853.2520325203253</v>
       </c>
       <c r="N15" t="n">
-        <v>10721</v>
+        <v>29122</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>21.16813430936688</v>
+        <v>24.23161418236754</v>
       </c>
       <c r="P15" t="n">
-        <v>4.25449161597129</v>
+        <v>7.374662152227485</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.131030647754507</v>
+        <v>7.885244396237145</v>
       </c>
       <c r="R15" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3352704278677314</v>
+        <v>0.3313791900054984</v>
       </c>
       <c r="T15" t="n">
-        <v>65.51452550032279</v>
+        <v>110.1736227045075</v>
       </c>
       <c r="U15" t="n">
-        <v>50.59</v>
+        <v>69.98</v>
       </c>
       <c r="V15" t="n">
-        <v>11.28</v>
+        <v>9.48</v>
       </c>
       <c r="W15" t="n">
-        <v>56.65</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
+          <t>Bajaj Finance Ltd</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.09416181067115</v>
+        <v>18.8419213518306</v>
       </c>
       <c r="D16" t="n">
-        <v>15.62719409629375</v>
+        <v>4.166013587646808</v>
       </c>
       <c r="E16" t="n">
-        <v>19.81565870053818</v>
+        <v>26.28792839991269</v>
       </c>
       <c r="F16" t="n">
-        <v>26.84289749881436</v>
+        <v>29.28581823473769</v>
       </c>
       <c r="G16" t="n">
-        <v>21.57040641689177</v>
+        <v>28.04336753256203</v>
       </c>
       <c r="H16" t="n">
-        <v>11.2650630655976</v>
+        <v>3.845990067652804</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05142381453500244</v>
+        <v>3.824788776468134</v>
       </c>
       <c r="J16" t="n">
-        <v>58.33193277310924</v>
+        <v>2689.166666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9027500384083577</v>
+        <v>16.30318653332505</v>
       </c>
       <c r="L16" t="n">
-        <v>11372</v>
+        <v>-79931</v>
       </c>
       <c r="M16" t="n">
-        <v>87.35596865878014</v>
+        <v>-496.4966768122243</v>
       </c>
       <c r="N16" t="n">
-        <v>12135</v>
+        <v>-72760</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>10.78116321985565</v>
+        <v>24.35264273954201</v>
       </c>
       <c r="P16" t="n">
-        <v>24.53682964293125</v>
+        <v>29.32313482597901</v>
       </c>
       <c r="Q16" t="n">
-        <v>29.45936165164078</v>
+        <v>27.5561392815338</v>
       </c>
       <c r="R16" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5684929901064378</v>
+        <v>0.1463025160881669</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08939726853647</v>
+        <v>16.91446153846154</v>
       </c>
       <c r="U16" t="n">
-        <v>37.9</v>
+        <v>69.2</v>
       </c>
       <c r="V16" t="n">
-        <v>6.71</v>
+        <v>4.11</v>
       </c>
       <c r="W16" t="n">
-        <v>56.25</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titan Company Ltd
-</t>
+          <t>Adani Green Energy Ltd</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37.2192057915469</v>
+        <v>12.81269066503966</v>
       </c>
       <c r="D17" t="n">
-        <v>18.8916977649372</v>
+        <v>7.249772398650458</v>
       </c>
       <c r="E17" t="n">
-        <v>6.843630099444054</v>
+        <v>13.66594360086768</v>
       </c>
       <c r="F17" t="n">
-        <v>10.35940803382664</v>
+        <v>79.3709327548807</v>
       </c>
       <c r="G17" t="n">
-        <v>9.21619293712317</v>
+        <v>58.73101952277657</v>
       </c>
       <c r="H17" t="n">
-        <v>11.08187783307446</v>
+        <v>1.430420271098699</v>
       </c>
       <c r="I17" t="n">
-        <v>1.653145959757266</v>
+        <v>6.595281675818589</v>
       </c>
       <c r="J17" t="n">
-        <v>9.411954765751211</v>
+        <v>1.713943268078306</v>
       </c>
       <c r="K17" t="n">
-        <v>2.491118669690098</v>
+        <v>8.655780267832741</v>
       </c>
       <c r="L17" t="n">
-        <v>1506</v>
+        <v>-13347</v>
       </c>
       <c r="M17" t="n">
-        <v>28.45804988662132</v>
+        <v>-182.3858977862804</v>
       </c>
       <c r="N17" t="n">
-        <v>1695</v>
+        <v>7713</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>20.89716395312024</v>
+        <v>34.97617292638284</v>
       </c>
       <c r="P17" t="n">
-        <v>20.27457629679304</v>
+        <v/>
       </c>
       <c r="Q17" t="n">
-        <v>19.50578386760935</v>
+        <v/>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.619298190002219</v>
+        <v>0.1046704357105556</v>
       </c>
       <c r="T17" t="n">
-        <v>13.77298463197627</v>
+        <v>0.1480315971999229</v>
       </c>
       <c r="U17" t="n">
-        <v>10.13</v>
+        <v>45.26</v>
       </c>
       <c r="V17" t="n">
-        <v>10.51</v>
+        <v>6.24</v>
       </c>
       <c r="W17" t="n">
-        <v>55.46</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd</t>
+          <t>Bajaj Finserv Ltd</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.99027109750765</v>
+        <v>25.85035141227954</v>
       </c>
       <c r="D18" t="n">
-        <v>5.11888931768417</v>
+        <v>11.44874463510097</v>
       </c>
       <c r="E18" t="n">
-        <v>28.8880112339828</v>
+        <v>14.12820930948886</v>
       </c>
       <c r="F18" t="n">
-        <v>62.41380175029464</v>
+        <v>37.04045949520755</v>
       </c>
       <c r="G18" t="n">
-        <v>61.20075729080469</v>
+        <v>36.22510916634958</v>
       </c>
       <c r="H18" t="n">
-        <v>1.949228933408289</v>
+        <v>2.901854246718086</v>
       </c>
       <c r="I18" t="n">
-        <v>6.445624336310825</v>
+        <v>4.789368120938867</v>
       </c>
       <c r="J18" t="n">
-        <v>1.300946133138182</v>
+        <v>2.197130112323319</v>
       </c>
       <c r="K18" t="n">
-        <v>8.274859381277622</v>
+        <v>2.948393092990266</v>
       </c>
       <c r="L18" t="n">
-        <v>12547</v>
+        <v>-79634</v>
       </c>
       <c r="M18" t="n">
-        <v>12.60245078344717</v>
+        <v>-194.7708261996772</v>
       </c>
       <c r="N18" t="n">
-        <v>157284</v>
+        <v>-68674</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>17.25086850260209</v>
+        <v>20.97274568418761</v>
       </c>
       <c r="P18" t="n">
-        <v>51.94877118224903</v>
+        <v>23.74781614270227</v>
       </c>
       <c r="Q18" t="n">
-        <v>55.18455739153598</v>
+        <v>20.58909506066124</v>
       </c>
       <c r="R18" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06747535915921023</v>
+        <v>0.2053943414307379</v>
       </c>
       <c r="T18" t="n">
-        <v>10.15120274914089</v>
+        <v>20.23501374885426</v>
       </c>
       <c r="U18" t="n">
-        <v>25.76</v>
+        <v>15.07</v>
       </c>
       <c r="V18" t="n">
-        <v>6.2</v>
+        <v>6.08</v>
       </c>
       <c r="W18" t="n">
-        <v>55.21</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adani Total Gas Ltd</t>
+          <t xml:space="preserve">Shriram Finance Ltd
+</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.65921787709497</v>
+        <v>15.11635033812082</v>
       </c>
       <c r="D19" t="n">
-        <v>18.41541755888651</v>
+        <v>4.064342198385718</v>
       </c>
       <c r="E19" t="n">
-        <v>14.92737430167598</v>
+        <v>20.33362647026492</v>
       </c>
       <c r="F19" t="n">
-        <v>24.67039106145252</v>
+        <v>28.9188743541827</v>
       </c>
       <c r="G19" t="n">
-        <v>21.13966480446927</v>
+        <v>27.30295701879741</v>
       </c>
       <c r="H19" t="n">
-        <v>10.13349514563107</v>
+        <v>2.980271160771109</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4349162011173184</v>
+        <v>3.994034363699512</v>
       </c>
       <c r="J19" t="n">
-        <v>10.5045045045045</v>
+        <v>0.6766743648960739</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7708333333333334</v>
+        <v>17.67784852228452</v>
       </c>
       <c r="L19" t="n">
-        <v/>
+        <v>-31359</v>
       </c>
       <c r="M19" t="n">
-        <v/>
+        <v>-298.0043713769838</v>
       </c>
       <c r="N19" t="n">
-        <v/>
+        <v>-31101</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>21.08864867789759</v>
+        <v>18.55607005277675</v>
       </c>
       <c r="P19" t="n">
-        <v>23.8762916927858</v>
+        <v>23.49387942502037</v>
       </c>
       <c r="Q19" t="n">
-        <v>24.57309396155174</v>
+        <v>14.28965514115608</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6788531553398058</v>
+        <v>0.1465685998082702</v>
       </c>
       <c r="T19" t="n">
-        <v>1.409892879647133</v>
+        <v>9.78698224852071</v>
       </c>
       <c r="U19" t="n">
-        <v>56.96</v>
+        <v>68.53</v>
       </c>
       <c r="V19" t="n">
-        <v>5.76</v>
+        <v>7.91</v>
       </c>
       <c r="W19" t="n">
-        <v>55.06</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd</t>
+          <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15.7230643179025</v>
+        <v>17.45521359669269</v>
       </c>
       <c r="D20" t="n">
-        <v>145.2287581699346</v>
+        <v>3.366695225484851</v>
       </c>
       <c r="E20" t="n">
-        <v>9.366915605017816</v>
+        <v>17.84689244899024</v>
       </c>
       <c r="F20" t="n">
-        <v>87.42129155073948</v>
+        <v>28.10102802275218</v>
       </c>
       <c r="G20" t="n">
-        <v>86.76721823595452</v>
+        <v>27.06778688096853</v>
       </c>
       <c r="H20" t="n">
-        <v>3.031212484993997</v>
+        <v>2.182709367780146</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002867677181482999</v>
+        <v>6.863420609401317</v>
       </c>
       <c r="J20" t="n">
-        <v>160.0267857142857</v>
+        <v>21.21176470588235</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.7107202680067</v>
+        <v>24.22265552460539</v>
       </c>
       <c r="L20" t="n">
-        <v>486</v>
+        <v>-38538</v>
       </c>
       <c r="M20" t="n">
-        <v>2.71356783919598</v>
+        <v>-715.6545961002786</v>
       </c>
       <c r="N20" t="n">
-        <v>2407</v>
+        <v>-35683</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>12.91184100336258</v>
+        <v>21.93916480497526</v>
       </c>
       <c r="P20" t="n">
-        <v>12.83917371819816</v>
+        <v>23.36341725167208</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.1392224868865</v>
+        <v>22.27523876455795</v>
       </c>
       <c r="R20" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3236083907247109</v>
+        <v>0.1223019286981607</v>
       </c>
       <c r="T20" t="n">
-        <v>22.02903225806451</v>
+        <v>12.26039667306462</v>
       </c>
       <c r="U20" t="n">
-        <v>49</v>
+        <v>16.79</v>
       </c>
       <c r="V20" t="n">
-        <v>7.86</v>
+        <v>10.36</v>
       </c>
       <c r="W20" t="n">
-        <v>54.91</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>HCL Technologies Ltd</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>23.01393141233172</v>
-      </c>
-      <c r="D21" t="n">
-        <v>27.05313357020305</v>
-      </c>
-      <c r="E21" t="n">
-        <v>14.29312274253273</v>
-      </c>
-      <c r="F21" t="n">
-        <v>22.01559415173819</v>
-      </c>
-      <c r="G21" t="n">
-        <v>18.21895499167524</v>
-      </c>
-      <c r="H21" t="n">
-        <v>15.86772518837242</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.08435023365512796</v>
-      </c>
-      <c r="J21" t="n">
-        <v>46.46112115732369</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-0.05698818084139185</v>
-      </c>
-      <c r="L21" t="n">
-        <v>15840</v>
-      </c>
-      <c r="M21" t="n">
-        <v>65.45995536821225</v>
-      </c>
-      <c r="N21" t="n">
-        <v>22448</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>12.71029997837341</v>
-      </c>
-      <c r="P21" t="n">
-        <v>9.194090295112023</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>9.407036350794119</v>
-      </c>
-      <c r="R21" t="n">
-        <v>90</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.110165040502596</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.13472891652169</v>
-      </c>
-      <c r="U21" t="n">
-        <v>63.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="W21" t="n">
-        <v>54.68</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Eicher Motors Ltd</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>22.17234691050152</v>
-      </c>
-      <c r="D22" t="n">
-        <v>20.20688908145581</v>
-      </c>
-      <c r="E22" t="n">
-        <v>24.19569424286405</v>
-      </c>
-      <c r="F22" t="n">
-        <v>26.17924528301887</v>
-      </c>
-      <c r="G22" t="n">
-        <v>22.56289308176101</v>
-      </c>
-      <c r="H22" t="n">
-        <v>17.30910664070949</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.02321972845663619</v>
-      </c>
-      <c r="J22" t="n">
-        <v>114.7058823529412</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-3.027951027951028</v>
-      </c>
-      <c r="L22" t="n">
-        <v>890</v>
-      </c>
-      <c r="M22" t="n">
-        <v>20.55902055902056</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3724</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>11.03693649673969</v>
-      </c>
-      <c r="P22" t="n">
-        <v>12.6758416653777</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>12.50545162905032</v>
-      </c>
-      <c r="R22" t="n">
-        <v>35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.7153796236210254</v>
-      </c>
-      <c r="T22" t="n">
-        <v>5.674673987645848</v>
-      </c>
-      <c r="U22" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="V22" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="W22" t="n">
-        <v>53.25</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dr Reddys Laboratories Ltd</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>19.74233736816026</v>
-      </c>
-      <c r="D23" t="n">
-        <v>21.36105235325225</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19.9136053693192</v>
-      </c>
-      <c r="F23" t="n">
-        <v>28.32101674342223</v>
-      </c>
-      <c r="G23" t="n">
-        <v>23.07307843347256</v>
-      </c>
-      <c r="H23" t="n">
-        <v>14.38370293965962</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.07085722375592836</v>
-      </c>
-      <c r="J23" t="n">
-        <v>51.70760233918129</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-0.3690911382831211</v>
-      </c>
-      <c r="L23" t="n">
-        <v>509</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.416235976301525</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4543</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>12.63964434957199</v>
-      </c>
-      <c r="P23" t="n">
-        <v>23.39250464543747</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>23.84240955838754</v>
-      </c>
-      <c r="R23" t="n">
-        <v>12</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.7223053120165034</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.686648762708613</v>
-      </c>
-      <c r="U23" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="V23" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="W23" t="n">
-        <v>51.95</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hindalco Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>9.567011474761177</v>
-      </c>
-      <c r="D24" t="n">
-        <v>113.5795251750748</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4.702216130615571</v>
-      </c>
-      <c r="F24" t="n">
-        <v>88.94620349876368</v>
-      </c>
-      <c r="G24" t="n">
-        <v>85.46364638223392</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4.401381743475944</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.5309290976579428</v>
-      </c>
-      <c r="J24" t="n">
-        <v>126.4654377880184</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.2129834973189651</v>
-      </c>
-      <c r="L24" t="n">
-        <v>9789</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.096048727159144</v>
-      </c>
-      <c r="N24" t="n">
-        <v>24056</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>10.59243381898591</v>
-      </c>
-      <c r="P24" t="n">
-        <v>13.06871230695661</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>13.39665776330272</v>
-      </c>
-      <c r="R24" t="n">
-        <v>8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.9360228499109322</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.931508809587693</v>
-      </c>
-      <c r="U24" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="V24" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="W24" t="n">
-        <v>50.69</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Pidilite Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>20.78030212917806</v>
-      </c>
-      <c r="D25" t="n">
-        <v>26.93139151211742</v>
-      </c>
-      <c r="E25" t="n">
-        <v>14.10805136073649</v>
-      </c>
-      <c r="F25" t="n">
-        <v>21.86869094726642</v>
-      </c>
-      <c r="G25" t="n">
-        <v>19.11491561011064</v>
-      </c>
-      <c r="H25" t="n">
-        <v>14.46671083140112</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.04543832520518615</v>
-      </c>
-      <c r="J25" t="n">
-        <v>54.33333333333334</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-0.6842688330871491</v>
-      </c>
-      <c r="L25" t="n">
-        <v>955</v>
-      </c>
-      <c r="M25" t="n">
-        <v>35.2658788774003</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2724</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>11.83637017589811</v>
-      </c>
-      <c r="P25" t="n">
-        <v>13.48774998597666</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>13.56415724960776</v>
-      </c>
-      <c r="R25" t="n">
-        <v>47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.025422325273269</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.271693267290405</v>
-      </c>
-      <c r="U25" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="V25" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>50.48</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bharti Airtel Ltd</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>10.35839213740181</v>
-      </c>
-      <c r="D26" t="n">
-        <v>12.99549647732646</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5.706018055499993</v>
-      </c>
-      <c r="F26" t="n">
-        <v>52.20093077836007</v>
-      </c>
-      <c r="G26" t="n">
-        <v>25.83910069208305</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.936115868322403</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.609472397390431</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.305545743553515</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.350048536248914</v>
-      </c>
-      <c r="L26" t="n">
-        <v>27809</v>
-      </c>
-      <c r="M26" t="n">
-        <v>35.51959331732489</v>
-      </c>
-      <c r="N26" t="n">
-        <v>78898</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>13.17410230151459</v>
-      </c>
-      <c r="P26" t="n">
-        <v>38.35662769365473</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>67.02776523348103</v>
-      </c>
-      <c r="R26" t="n">
-        <v>62</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.3393112060793767</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.4944956034064945</v>
-      </c>
-      <c r="U26" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="W26" t="n">
-        <v>49.74</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DMART</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Avenue Supermarts Ltd</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>13.56294790886726</v>
-      </c>
-      <c r="D27" t="n">
-        <v>17.49611197511664</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4.993207190533383</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8.084427730414067</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6.645139695603379</v>
-      </c>
-      <c r="H27" t="n">
-        <v>11.97808426223314</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.03166114022890149</v>
-      </c>
-      <c r="J27" t="n">
-        <v>73.29310344827586</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.1181198246468583</v>
-      </c>
-      <c r="L27" t="n">
-        <v>278</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.770579639551875</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2746</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>20.48312440202782</v>
-      </c>
-      <c r="P27" t="n">
-        <v>22.96698996520703</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>22.74033782145131</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.398875873795579</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.785985836749907</v>
-      </c>
-      <c r="U27" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="V27" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="W27" t="n">
-        <v>49.48</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>State Bank of India</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v/>
-      </c>
-      <c r="D28" t="n">
-        <v/>
-      </c>
-      <c r="E28" t="n">
-        <v>15.83441297482405</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-13.72916899102664</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-14.60555706085535</v>
-      </c>
-      <c r="H28" t="n">
-        <v/>
-      </c>
-      <c r="I28" t="n">
-        <v/>
-      </c>
-      <c r="J28" t="n">
-        <v>0.3660986540179259</v>
-      </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v>18156</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-30.11095079357182</v>
-      </c>
-      <c r="N28" t="n">
-        <v>21632</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>11.63380022632805</v>
-      </c>
-      <c r="P28" t="n">
-        <v>83.40695423292949</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>90.36539387158786</v>
-      </c>
-      <c r="R28" t="n">
-        <v>18</v>
-      </c>
-      <c r="S28" t="n">
-        <v/>
-      </c>
-      <c r="T28" t="n">
-        <v/>
-      </c>
-      <c r="U28" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="W28" t="n">
-        <v>49.16</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Apollo Hospitals
-Chain of Indian private hospitals</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>13.48039215686275</v>
-      </c>
-      <c r="D29" t="n">
-        <v>13.91311435324802</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4.905818773282963</v>
-      </c>
-      <c r="F29" t="n">
-        <v>12.56099480560365</v>
-      </c>
-      <c r="G29" t="n">
-        <v>8.956398551865261</v>
-      </c>
-      <c r="H29" t="n">
-        <v>5.584756898817345</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.7688869665513264</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.565701559020044</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.815789473684211</v>
-      </c>
-      <c r="L29" t="n">
-        <v>383</v>
-      </c>
-      <c r="M29" t="n">
-        <v>15.99832915622389</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1920</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>14.66004260219314</v>
-      </c>
-      <c r="P29" t="n">
-        <v>36.13077689773863</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>29.95061094416296</v>
-      </c>
-      <c r="R29" t="n">
-        <v>26</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.138394457054115</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.972164735099338</v>
-      </c>
-      <c r="U29" t="n">
-        <v>47.72</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="W29" t="n">
-        <v>48.27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Canara Bank</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>16.71605179468811</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3.09484900948278</v>
-      </c>
-      <c r="E30" t="n">
-        <v>13.93516047014541</v>
-      </c>
-      <c r="F30" t="n">
-        <v>41.75390656810141</v>
-      </c>
-      <c r="G30" t="n">
-        <v>40.93775730869805</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.003310710363005</v>
-      </c>
-      <c r="I30" t="n">
-        <v>14.86741992554242</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.610661174334986</v>
-      </c>
-      <c r="K30" t="n">
-        <v>21.03265721839379</v>
-      </c>
-      <c r="L30" t="n">
-        <v>13296</v>
-      </c>
-      <c r="M30" t="n">
-        <v>28.81289819269276</v>
-      </c>
-      <c r="N30" t="n">
-        <v>15046</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>18.17561078322378</v>
-      </c>
-      <c r="P30" t="n">
-        <v>85.7752850068174</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>53.4206382524911</v>
-      </c>
-      <c r="R30" t="n">
-        <v>19</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.0719985042520674</v>
-      </c>
-      <c r="T30" t="n">
-        <v>8.96269564512205</v>
-      </c>
-      <c r="U30" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="V30" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="W30" t="n">
-        <v>47.52</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>HDFC Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>14.33974005030719</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4.801033923800871</v>
-      </c>
-      <c r="E31" t="n">
-        <v>23.07288232992184</v>
-      </c>
-      <c r="F31" t="n">
-        <v>61.41252040373843</v>
-      </c>
-      <c r="G31" t="n">
-        <v>60.32244076305575</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.623892050854127</v>
-      </c>
-      <c r="I31" t="n">
-        <v>6.808786667718385</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1.400768822479211</v>
-      </c>
-      <c r="K31" t="n">
-        <v>12.06583962892374</v>
-      </c>
-      <c r="L31" t="n">
-        <v>35669</v>
-      </c>
-      <c r="M31" t="n">
-        <v>20.47635996234127</v>
-      </c>
-      <c r="N31" t="n">
-        <v>19069</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>21.95098428169122</v>
-      </c>
-      <c r="P31" t="n">
-        <v>23.86506357287907</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>15.42478808253083</v>
-      </c>
-      <c r="R31" t="n">
-        <v>23</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.07038097917866981</v>
-      </c>
-      <c r="T31" t="n">
-        <v>22.50468105363377</v>
-      </c>
-      <c r="U31" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>47.51</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Indian Railway Finance Corporation Ltd</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>13.0380853616381</v>
-      </c>
-      <c r="D32" t="n">
-        <v>5.746523336036321</v>
-      </c>
-      <c r="E32" t="n">
-        <v>24.0645524488647</v>
-      </c>
-      <c r="F32" t="n">
-        <v>99.50459748545694</v>
-      </c>
-      <c r="G32" t="n">
-        <v>99.47082004128355</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.321838369595244</v>
-      </c>
-      <c r="I32" t="n">
-        <v>8.378352548852153</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.31948659270683</v>
-      </c>
-      <c r="K32" t="n">
-        <v>15.53898087730547</v>
-      </c>
-      <c r="L32" t="n">
-        <v>7906</v>
-      </c>
-      <c r="M32" t="n">
-        <v>29.81933391166598</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7914</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>19.06740855567788</v>
-      </c>
-      <c r="P32" t="n">
-        <v>23.24502393394037</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>20.11244339814313</v>
-      </c>
-      <c r="R32" t="n">
-        <v>31</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.05492885738906</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1211.136363636364</v>
-      </c>
-      <c r="U32" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="V32" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="W32" t="n">
-        <v>46.28</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kotak Mahindra Bank Ltd
-</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>14.01301818853291</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.113136699541475</v>
-      </c>
-      <c r="E33" t="n">
-        <v>32.38615146611662</v>
-      </c>
-      <c r="F33" t="n">
-        <v>83.66733645109092</v>
-      </c>
-      <c r="G33" t="n">
-        <v>82.2590109714245</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2.372513081844081</v>
-      </c>
-      <c r="I33" t="n">
-        <v>4.003739266919029</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1.236375108447038</v>
-      </c>
-      <c r="K33" t="n">
-        <v>5.821814163053642</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6766</v>
-      </c>
-      <c r="M33" t="n">
-        <v>14.37983507608603</v>
-      </c>
-      <c r="N33" t="n">
-        <v>15685</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>13.51960376324537</v>
-      </c>
-      <c r="P33" t="n">
-        <v>20.38200065626572</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>19.34407044160125</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.07325702420450533</v>
-      </c>
-      <c r="T33" t="n">
-        <v>16.02193732193732</v>
-      </c>
-      <c r="U33" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W33" t="n">
-        <v>46.15</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Maruti Suzuki India Ltd</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>15.75038535195478</v>
-      </c>
-      <c r="D34" t="n">
-        <v>15.59092764270305</v>
-      </c>
-      <c r="E34" t="n">
-        <v>9.50809964894472</v>
-      </c>
-      <c r="F34" t="n">
-        <v>13.13003143989059</v>
-      </c>
-      <c r="G34" t="n">
-        <v>9.4249178756221</v>
-      </c>
-      <c r="H34" t="n">
-        <v>11.69777284396031</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.001389602503619973</v>
-      </c>
-      <c r="J34" t="n">
-        <v>117.9072164948454</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-3.069741221947815</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4936</v>
-      </c>
-      <c r="M34" t="n">
-        <v>26.50059057231827</v>
-      </c>
-      <c r="N34" t="n">
-        <v>16801</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>10.51021511264258</v>
-      </c>
-      <c r="P34" t="n">
-        <v>12.00718203930038</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>11.1392224868865</v>
-      </c>
-      <c r="R34" t="n">
-        <v>29</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.230295566502463</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5.090902565942939</v>
-      </c>
-      <c r="U34" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="V34" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="W34" t="n">
-        <v>45.51</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Punjab National Bank</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>61.32056519118731</v>
-      </c>
-      <c r="D35" t="n">
-        <v/>
-      </c>
-      <c r="E35" t="n">
-        <v>8.395910695456838</v>
-      </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
-      <c r="G35" t="n">
-        <v/>
-      </c>
-      <c r="H35" t="n">
-        <v>12.65285818905363</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3.684256345007701</v>
-      </c>
-      <c r="J35" t="n">
-        <v/>
-      </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v>-29445</v>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v>-27939</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>15.90207600910603</v>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
-      <c r="Q35" t="n">
-        <v/>
-      </c>
-      <c r="R35" t="n">
-        <v>18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.50702629506294</v>
-      </c>
-      <c r="T35" t="n">
-        <v>529.4417475728155</v>
-      </c>
-      <c r="U35" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="V35" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="W35" t="n">
-        <v>43.79</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Tata Consumer Products Ltd</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>7.566793298872766</v>
-      </c>
-      <c r="D36" t="n">
-        <v>9.762465444865363</v>
-      </c>
-      <c r="E36" t="n">
-        <v>7.990266999868473</v>
-      </c>
-      <c r="F36" t="n">
-        <v>15.02038668946468</v>
-      </c>
-      <c r="G36" t="n">
-        <v>12.54110219650138</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4.358119014311847</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.21654107242947</v>
-      </c>
-      <c r="J36" t="n">
-        <v>25.32183908045977</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1.140980735551664</v>
-      </c>
-      <c r="L36" t="n">
-        <v>26</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.138353765323993</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1937</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>15.96086282879563</v>
-      </c>
-      <c r="P36" t="n">
-        <v>21.59956338772886</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>14.86983549970351</v>
-      </c>
-      <c r="R36" t="n">
-        <v>64</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.5454284586965099</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.7855150325446844</v>
-      </c>
-      <c r="U36" t="n">
-        <v>54.79</v>
-      </c>
-      <c r="V36" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="W36" t="n">
-        <v>43.31</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tata Power Company Ltd
-</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>13.22784027691927</v>
-      </c>
-      <c r="D37" t="n">
-        <v>8.076006740658958</v>
-      </c>
-      <c r="E37" t="n">
-        <v>6.965125551270159</v>
-      </c>
-      <c r="F37" t="n">
-        <v>17.46977168058065</v>
-      </c>
-      <c r="G37" t="n">
-        <v>11.30856482611597</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.077940943806003</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.659321300531586</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.054392402331103</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3.48141592920354</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3569</v>
-      </c>
-      <c r="M37" t="n">
-        <v>33.24639031206335</v>
-      </c>
-      <c r="N37" t="n">
-        <v>12596</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>15.51115820187641</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10.431728917459</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.922384104881218</v>
-      </c>
-      <c r="R37" t="n">
-        <v>17</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.4419074604110633</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.9142835887516738</v>
-      </c>
-      <c r="U37" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="W37" t="n">
-        <v>43.1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Havells India Ltd</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>17.06727541291795</v>
-      </c>
-      <c r="D38" t="n">
-        <v>19.90967741935484</v>
-      </c>
-      <c r="E38" t="n">
-        <v>6.837009144701453</v>
-      </c>
-      <c r="F38" t="n">
-        <v>10.11834319526627</v>
-      </c>
-      <c r="G38" t="n">
-        <v>8.300161377084454</v>
-      </c>
-      <c r="H38" t="n">
-        <v>10.22279417678758</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.040687525177924</v>
-      </c>
-      <c r="J38" t="n">
-        <v>25.35714285714286</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.1504518872939926</v>
-      </c>
-      <c r="L38" t="n">
-        <v>335</v>
-      </c>
-      <c r="M38" t="n">
-        <v>17.80967570441255</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1953</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>13.03790793906312</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10.03323122942004</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>8.997698704834534</v>
-      </c>
-      <c r="R38" t="n">
-        <v>44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.495214348910158</v>
-      </c>
-      <c r="T38" t="n">
-        <v>4.66148445336008</v>
-      </c>
-      <c r="U38" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="V38" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="W38" t="n">
-        <v>43.1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Info Edge (India) Ltd</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1.96616218359659</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.999475547397404</v>
-      </c>
-      <c r="E39" t="n">
-        <v>23.46214511041009</v>
-      </c>
-      <c r="F39" t="n">
-        <v>28.03627760252366</v>
-      </c>
-      <c r="G39" t="n">
-        <v>24.05362776025236</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.648701820499321</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.008129006675038002</v>
-      </c>
-      <c r="J39" t="n">
-        <v>28.97142857142857</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-43.54008438818565</v>
-      </c>
-      <c r="L39" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M39" t="n">
-        <v>-21.09704641350211</v>
-      </c>
-      <c r="N39" t="n">
-        <v>702</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>17.11561008996074</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.1011465318701221</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>-2.129609917599939</v>
-      </c>
-      <c r="R39" t="n">
-        <v>49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.07027071960985341</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.130864197530864</v>
-      </c>
-      <c r="U39" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="V39" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="W39" t="n">
-        <v>42.85</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Adani Energy Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>9.461276797721698</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7.915753052644284</v>
-      </c>
-      <c r="E40" t="n">
-        <v>7.201782380923707</v>
-      </c>
-      <c r="F40" t="n">
-        <v>34.38911302462817</v>
-      </c>
-      <c r="G40" t="n">
-        <v>23.69482748238694</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.043117291332126</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.93252116130053</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.284784965666787</v>
-      </c>
-      <c r="K40" t="n">
-        <v>6.356855191735248</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1095</v>
-      </c>
-      <c r="M40" t="n">
-        <v>19.17352477674663</v>
-      </c>
-      <c r="N40" t="n">
-        <v>6038</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>17.85124994851739</v>
-      </c>
-      <c r="P40" t="n">
-        <v>16.42972571572392</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>14.86983549970351</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.2836960606785336</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0.4266957862281603</v>
-      </c>
-      <c r="U40" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="W40" t="n">
-        <v>41.72</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Adani Enterprises Ltd</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>8.534650424813185</v>
-      </c>
-      <c r="D41" t="n">
-        <v>7.984787232004292</v>
-      </c>
-      <c r="E41" t="n">
-        <v>3.458790097592848</v>
-      </c>
-      <c r="F41" t="n">
-        <v>11.79929683367731</v>
-      </c>
-      <c r="G41" t="n">
-        <v>8.644382447807013</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2.076768834144944</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.671358378544375</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.749286498353458</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.975740529137734</v>
-      </c>
-      <c r="L41" t="n">
-        <v>-8455</v>
-      </c>
-      <c r="M41" t="n">
-        <v>-74.31660367407929</v>
-      </c>
-      <c r="N41" t="n">
-        <v>10312</v>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>19.01541475308124</v>
-      </c>
-      <c r="P41" t="n">
-        <v>45.81058899665285</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>31.95079107728942</v>
-      </c>
-      <c r="R41" t="n">
-        <v>5</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.6004321671876751</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1.461411379550759</v>
-      </c>
-      <c r="U41" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="V41" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="W41" t="n">
-        <v>41.16</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SHREECEM</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Shree Cement Ltd</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>8.370767521615225</v>
-      </c>
-      <c r="D42" t="n">
-        <v>11.72234894226039</v>
-      </c>
-      <c r="E42" t="n">
-        <v>8.445007553238145</v>
-      </c>
-      <c r="F42" t="n">
-        <v>22.01647093221578</v>
-      </c>
-      <c r="G42" t="n">
-        <v>12.77228205253155</v>
-      </c>
-      <c r="H42" t="n">
-        <v>6.205908683974934</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.07998840747717723</v>
-      </c>
-      <c r="J42" t="n">
-        <v>19.82558139534884</v>
-      </c>
-      <c r="K42" t="n">
-        <v>-1.305887560867641</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1929</v>
-      </c>
-      <c r="M42" t="n">
-        <v>42.69588313413015</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3347</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>10.32561591555659</v>
-      </c>
-      <c r="P42" t="n">
-        <v>11.2926552609119</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>10.67987982673917</v>
-      </c>
-      <c r="R42" t="n">
-        <v>16</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.7348612354521038</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.139610051089563</v>
-      </c>
-      <c r="U42" t="n">
-        <v>25.87</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W42" t="n">
-        <v>40.76</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NTPC Ltd</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>13.27359840706863</v>
-      </c>
-      <c r="D43" t="n">
-        <v>8.860826310008269</v>
-      </c>
-      <c r="E43" t="n">
-        <v>11.95063332978527</v>
-      </c>
-      <c r="F43" t="n">
-        <v>28.82672926202094</v>
-      </c>
-      <c r="G43" t="n">
-        <v>19.74890896969765</v>
-      </c>
-      <c r="H43" t="n">
-        <v>4.450861504179203</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.475521125007778</v>
-      </c>
-      <c r="J43" t="n">
-        <v>4.604991464108609</v>
-      </c>
-      <c r="K43" t="n">
-        <v>4.29971237562189</v>
-      </c>
-      <c r="L43" t="n">
-        <v>8644</v>
-      </c>
-      <c r="M43" t="n">
-        <v>16.7988184079602</v>
-      </c>
-      <c r="N43" t="n">
-        <v>40785</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>12.22230965433799</v>
-      </c>
-      <c r="P43" t="n">
-        <v>8.735165684951163</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>8.447177119769854</v>
-      </c>
-      <c r="R43" t="n">
-        <v>36</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.3724372910920176</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0.6893687194420199</v>
-      </c>
-      <c r="U43" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="V43" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="W43" t="n">
-        <v>40.71</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>GAIL (India) Ltd</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>12.86154006000234</v>
-      </c>
-      <c r="D44" t="n">
-        <v>10.77223633731818</v>
-      </c>
-      <c r="E44" t="n">
-        <v>7.433122166511544</v>
-      </c>
-      <c r="F44" t="n">
-        <v>10.74398775032275</v>
-      </c>
-      <c r="G44" t="n">
-        <v>7.987810370192452</v>
-      </c>
-      <c r="H44" t="n">
-        <v>7.939231170080571</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.2830499889606088</v>
-      </c>
-      <c r="J44" t="n">
-        <v>23.62447844228095</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.008103954170741931</v>
-      </c>
-      <c r="L44" t="n">
-        <v>4360</v>
-      </c>
-      <c r="M44" t="n">
-        <v>30.45968981416794</v>
-      </c>
-      <c r="N44" t="n">
-        <v>12586</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>11.82515452182427</v>
-      </c>
-      <c r="P44" t="n">
-        <v>8.608876760374562</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>8.447177119769854</v>
-      </c>
-      <c r="R44" t="n">
-        <v>37</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1.068088347296268</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.414075523664565</v>
-      </c>
-      <c r="U44" t="n">
-        <v>25.84</v>
-      </c>
-      <c r="V44" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="W44" t="n">
-        <v>40.39</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SBI Life Insurance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>12.70458814059566</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.140327341024953</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1.434978937479165</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.1863805800527321</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.1287995878413189</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.4755221579767963</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>240.3333333333333</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-1564.808943089431</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-2099</v>
-      </c>
-      <c r="M45" t="n">
-        <v>-853.2520325203253</v>
-      </c>
-      <c r="N45" t="n">
-        <v>29122</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>24.23161418236754</v>
-      </c>
-      <c r="P45" t="n">
-        <v>7.374662152227485</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>7.885244396237145</v>
-      </c>
-      <c r="R45" t="n">
-        <v>14</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0.3313791900054984</v>
-      </c>
-      <c r="T45" t="n">
-        <v>110.1736227045075</v>
-      </c>
-      <c r="U45" t="n">
-        <v>69.98</v>
-      </c>
-      <c r="V45" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="W45" t="n">
-        <v>39.23</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ICICI Prudential Life Insurance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>7.732848705134029</v>
-      </c>
-      <c r="D46" t="n">
-        <v>753.9778779188856</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.942341125272681</v>
-      </c>
-      <c r="F46" t="n">
-        <v>102.0253136523193</v>
-      </c>
-      <c r="G46" t="n">
-        <v>101.9001849247567</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.2846144327276497</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.1090413448432531</v>
-      </c>
-      <c r="J46" t="n">
-        <v>31.02154882154882</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-3.131544673091951</v>
-      </c>
-      <c r="L46" t="n">
-        <v>105</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.1139619692628289</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-7315</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>16.84553965244746</v>
-      </c>
-      <c r="P46" t="n">
-        <v>-5.663194189152343</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-5.591248870509801</v>
-      </c>
-      <c r="R46" t="n">
-        <v>10</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.3020290902037117</v>
-      </c>
-      <c r="T46" t="n">
-        <v>134.7865671641791</v>
-      </c>
-      <c r="U46" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="V46" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="W46" t="n">
-        <v>39.22</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Bajaj Finance Ltd</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>18.8419213518306</v>
-      </c>
-      <c r="D47" t="n">
-        <v>4.166013587646808</v>
-      </c>
-      <c r="E47" t="n">
-        <v>26.28792839991269</v>
-      </c>
-      <c r="F47" t="n">
-        <v>29.28581823473769</v>
-      </c>
-      <c r="G47" t="n">
-        <v>28.04336753256203</v>
-      </c>
-      <c r="H47" t="n">
-        <v>3.845990067652804</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3.824788776468134</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2689.166666666667</v>
-      </c>
-      <c r="K47" t="n">
-        <v>16.30318653332505</v>
-      </c>
-      <c r="L47" t="n">
-        <v>-79931</v>
-      </c>
-      <c r="M47" t="n">
-        <v>-496.4966768122243</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-72760</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>24.35264273954201</v>
-      </c>
-      <c r="P47" t="n">
-        <v>29.32313482597901</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>27.5561392815338</v>
-      </c>
-      <c r="R47" t="n">
-        <v>15</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.1463025160881669</v>
-      </c>
-      <c r="T47" t="n">
-        <v>16.91446153846154</v>
-      </c>
-      <c r="U47" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="V47" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="W47" t="n">
-        <v>39.18</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Bank of Baroda</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>15.7618637908999</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.712278690337432</v>
-      </c>
-      <c r="E48" t="n">
-        <v>15.93948250956673</v>
-      </c>
-      <c r="F48" t="n">
-        <v>37.4889127294537</v>
-      </c>
-      <c r="G48" t="n">
-        <v>36.05115772223114</v>
-      </c>
-      <c r="H48" t="n">
-        <v>1.140275868320467</v>
-      </c>
-      <c r="I48" t="n">
-        <v>12.14371872728943</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.896747724261721</v>
-      </c>
-      <c r="K48" t="n">
-        <v>23.58378963023052</v>
-      </c>
-      <c r="L48" t="n">
-        <v>-7559</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-17.03283084341693</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-6274</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>17.47729766589094</v>
-      </c>
-      <c r="P48" t="n">
-        <v>74.50588066551305</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>55.18455739153598</v>
-      </c>
-      <c r="R48" t="n">
-        <v>21</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.07153782236255685</v>
-      </c>
-      <c r="T48" t="n">
-        <v>13.0747735807378</v>
-      </c>
-      <c r="U48" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="V48" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W48" t="n">
-        <v>39.09</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Axis Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>15.83271240518905</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.520716781712082</v>
-      </c>
-      <c r="E49" t="n">
-        <v>22.73130411725443</v>
-      </c>
-      <c r="F49" t="n">
-        <v>34.69264599658038</v>
-      </c>
-      <c r="G49" t="n">
-        <v>33.47292194314659</v>
-      </c>
-      <c r="H49" t="n">
-        <v>1.637489222711312</v>
-      </c>
-      <c r="I49" t="n">
-        <v>8.249122739980766</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.691203992514036</v>
-      </c>
-      <c r="K49" t="n">
-        <v>25.37880504967978</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-14556</v>
-      </c>
-      <c r="M49" t="n">
-        <v>-38.36280736894816</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-5555</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>14.74358712051438</v>
-      </c>
-      <c r="P49" t="n">
-        <v>39.67228711897934</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>35.09600385206135</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.0720367478374617</v>
-      </c>
-      <c r="T49" t="n">
-        <v>18.66365187713311</v>
-      </c>
-      <c r="U49" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="V49" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="W49" t="n">
-        <v>37.55</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>JSWSTEEL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>JSW Steel Ltd</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>11.5528718021347</v>
-      </c>
-      <c r="D50" t="n">
-        <v>12.06437553198553</v>
-      </c>
-      <c r="E50" t="n">
-        <v>5.127252779904689</v>
-      </c>
-      <c r="F50" t="n">
-        <v>16.08916265728032</v>
-      </c>
-      <c r="G50" t="n">
-        <v>11.41960847056672</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3.937287733986257</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1.132807168883338</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.659099321406539</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2.867421955464005</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="M50" t="n">
-        <v>-8.484568668537131</v>
-      </c>
-      <c r="N50" t="n">
-        <v>12078</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>15.60469505245279</v>
-      </c>
-      <c r="P50" t="n">
-        <v>3.585216043903361</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.383625553960966</v>
-      </c>
-      <c r="R50" t="n">
-        <v>25</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.7679137157851319</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.556148353651488</v>
-      </c>
-      <c r="U50" t="n">
-        <v>69.27</v>
-      </c>
-      <c r="V50" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="W50" t="n">
-        <v>34.84</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>TVS Motor Company Ltd</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>26.22346698113208</v>
-      </c>
-      <c r="D51" t="n">
-        <v>13.79993900579445</v>
-      </c>
-      <c r="E51" t="n">
-        <v>4.544641716694342</v>
-      </c>
-      <c r="F51" t="n">
-        <v>14.05032571209605</v>
-      </c>
-      <c r="G51" t="n">
-        <v>11.55958615404266</v>
-      </c>
-      <c r="H51" t="n">
-        <v>4.233295259851514</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.833431603773585</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.907676348547718</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.524181818181818</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-2254</v>
-      </c>
-      <c r="M51" t="n">
-        <v>-40.98181818181818</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-1253</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>14.19238770427707</v>
-      </c>
-      <c r="P51" t="n">
-        <v>19.6651221066765</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>19.13578981670916</v>
-      </c>
-      <c r="R51" t="n">
-        <v>23</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.9314915286502951</v>
-      </c>
-      <c r="T51" t="n">
-        <v>6.644882023425565</v>
-      </c>
-      <c r="U51" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="W51" t="n">
-        <v>34.06</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Adani Green Energy Ltd</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>12.81269066503966</v>
-      </c>
-      <c r="D52" t="n">
-        <v>7.249772398650458</v>
-      </c>
-      <c r="E52" t="n">
-        <v>13.66594360086768</v>
-      </c>
-      <c r="F52" t="n">
-        <v>79.3709327548807</v>
-      </c>
-      <c r="G52" t="n">
-        <v>58.73101952277657</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.430420271098699</v>
-      </c>
-      <c r="I52" t="n">
-        <v>6.595281675818589</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.713943268078306</v>
-      </c>
-      <c r="K52" t="n">
-        <v>8.655780267832741</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-13347</v>
-      </c>
-      <c r="M52" t="n">
-        <v>-182.3858977862804</v>
-      </c>
-      <c r="N52" t="n">
-        <v>7713</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>34.97617292638284</v>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
-      <c r="Q52" t="n">
-        <v/>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.1046704357105556</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0.1480315971999229</v>
-      </c>
-      <c r="U52" t="n">
-        <v>45.26</v>
-      </c>
-      <c r="V52" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="W52" t="n">
-        <v>29.36</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BAJAJFINSV</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Bajaj Finserv Ltd</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>25.85035141227954</v>
-      </c>
-      <c r="D53" t="n">
-        <v>11.44874463510097</v>
-      </c>
-      <c r="E53" t="n">
-        <v>14.12820930948886</v>
-      </c>
-      <c r="F53" t="n">
-        <v>37.04045949520755</v>
-      </c>
-      <c r="G53" t="n">
-        <v>36.22510916634958</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.901854246718086</v>
-      </c>
-      <c r="I53" t="n">
-        <v>4.789368120938867</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.197130112323319</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.948393092990266</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-79634</v>
-      </c>
-      <c r="M53" t="n">
-        <v>-194.7708261996772</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-68674</v>
-      </c>
-      <c r="O53" s="2" t="n">
-        <v>20.97274568418761</v>
-      </c>
-      <c r="P53" t="n">
-        <v>23.74781614270227</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>20.58909506066124</v>
-      </c>
-      <c r="R53" t="n">
-        <v>2</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0.2053943414307379</v>
-      </c>
-      <c r="T53" t="n">
-        <v>20.23501374885426</v>
-      </c>
-      <c r="U53" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="W53" t="n">
-        <v>29.33</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shriram Finance Ltd
-</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>15.11635033812082</v>
-      </c>
-      <c r="D54" t="n">
-        <v>4.064342198385718</v>
-      </c>
-      <c r="E54" t="n">
-        <v>20.33362647026492</v>
-      </c>
-      <c r="F54" t="n">
-        <v>28.9188743541827</v>
-      </c>
-      <c r="G54" t="n">
-        <v>27.30295701879741</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2.980271160771109</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3.994034363699512</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.6766743648960739</v>
-      </c>
-      <c r="K54" t="n">
-        <v>17.67784852228452</v>
-      </c>
-      <c r="L54" t="n">
-        <v>-31359</v>
-      </c>
-      <c r="M54" t="n">
-        <v>-298.0043713769838</v>
-      </c>
-      <c r="N54" t="n">
-        <v>-31101</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>18.55607005277675</v>
-      </c>
-      <c r="P54" t="n">
-        <v>23.49387942502037</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>14.28965514115608</v>
-      </c>
-      <c r="R54" t="n">
-        <v>23</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0.1465685998082702</v>
-      </c>
-      <c r="T54" t="n">
-        <v>9.78698224852071</v>
-      </c>
-      <c r="U54" t="n">
-        <v>68.53</v>
-      </c>
-      <c r="V54" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="W54" t="n">
-        <v>26.64</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Grasim Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>11.19646261265834</v>
-      </c>
-      <c r="D55" t="n">
-        <v>9.828704031743781</v>
-      </c>
-      <c r="E55" t="n">
-        <v>7.578371940325857</v>
-      </c>
-      <c r="F55" t="n">
-        <v>20.76302890561774</v>
-      </c>
-      <c r="G55" t="n">
-        <v>16.94483042953778</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2.408545166894758</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.547099364939709</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.015845639754231</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.2886192314763744</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-33833</v>
-      </c>
-      <c r="M55" t="n">
-        <v>-124.408898694613</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-10719</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>11.15172597339149</v>
-      </c>
-      <c r="P55" t="n">
-        <v>29.31424972932857</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>27.73084445875398</v>
-      </c>
-      <c r="R55" t="n">
-        <v>12</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0.3178182841724175</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.303341493024459</v>
-      </c>
-      <c r="U55" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="V55" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="W55" t="n">
-        <v>24.96</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>17.45521359669269</v>
-      </c>
-      <c r="D56" t="n">
-        <v>3.366695225484851</v>
-      </c>
-      <c r="E56" t="n">
-        <v>17.84689244899024</v>
-      </c>
-      <c r="F56" t="n">
-        <v>28.10102802275218</v>
-      </c>
-      <c r="G56" t="n">
-        <v>27.06778688096853</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2.182709367780146</v>
-      </c>
-      <c r="I56" t="n">
-        <v>6.863420609401317</v>
-      </c>
-      <c r="J56" t="n">
-        <v>21.21176470588235</v>
-      </c>
-      <c r="K56" t="n">
-        <v>24.22265552460539</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-38538</v>
-      </c>
-      <c r="M56" t="n">
-        <v>-715.6545961002786</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-35683</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>21.93916480497526</v>
-      </c>
-      <c r="P56" t="n">
-        <v>23.36341725167208</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>22.27523876455795</v>
-      </c>
-      <c r="R56" t="n">
-        <v>5</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.1223019286981607</v>
-      </c>
-      <c r="T56" t="n">
-        <v>12.26039667306462</v>
-      </c>
-      <c r="U56" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="V56" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="W56" t="n">
         <v>24.85</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>IndusInd Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>14.25227319776422</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3.475962286021232</v>
-      </c>
-      <c r="E57" t="n">
-        <v>19.56369677362945</v>
-      </c>
-      <c r="F57" t="n">
-        <v>38.55469091544986</v>
-      </c>
-      <c r="G57" t="n">
-        <v>37.62568855469092</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.738083447425403</v>
-      </c>
-      <c r="I57" t="n">
-        <v>6.885742949503957</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.879527055815935</v>
-      </c>
-      <c r="K57" t="n">
-        <v>18.47584760176891</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-17468</v>
-      </c>
-      <c r="M57" t="n">
-        <v>-99.03617190157614</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-16843</v>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>15.49561308335803</v>
-      </c>
-      <c r="P57" t="n">
-        <v>22.07746495394836</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>15.89562187541786</v>
-      </c>
-      <c r="R57" t="n">
-        <v>14</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.08884228106460039</v>
-      </c>
-      <c r="T57" t="n">
-        <v>22.86256871564218</v>
-      </c>
-      <c r="U57" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="V57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W57" t="n">
-        <v>24.28</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>REC Ltd</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>20.39653929343908</v>
-      </c>
-      <c r="D58" t="n">
-        <v>9.294489608054098</v>
-      </c>
-      <c r="E58" t="n">
-        <v>29.7682934528695</v>
-      </c>
-      <c r="F58" t="n">
-        <v>100.7702506471368</v>
-      </c>
-      <c r="G58" t="n">
-        <v>100.7197424079803</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2.580305039666831</v>
-      </c>
-      <c r="I58" t="n">
-        <v>6.424917087238645</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.600474155202351</v>
-      </c>
-      <c r="K58" t="n">
-        <v>9.193576008186621</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-59554</v>
-      </c>
-      <c r="M58" t="n">
-        <v>-124.3739949460142</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-57723</v>
-      </c>
-      <c r="O58" s="2" t="n">
-        <v>13.33804224786568</v>
-      </c>
-      <c r="P58" t="n">
-        <v>19.76311435023079</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>19.67245924901726</v>
-      </c>
-      <c r="R58" t="n">
-        <v>30</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.08667964267928514</v>
-      </c>
-      <c r="T58" t="n">
-        <v>75.18512658227849</v>
-      </c>
-      <c r="U58" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="V58" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="W58" t="n">
-        <v>24.28</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Power Finance Corporation Ltd</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>26.1609340860332</v>
-      </c>
-      <c r="D59" t="n">
-        <v>3.480398875307857</v>
-      </c>
-      <c r="E59" t="n">
-        <v>28.91659745596014</v>
-      </c>
-      <c r="F59" t="n">
-        <v>36.68859553263103</v>
-      </c>
-      <c r="G59" t="n">
-        <v>36.63067709927001</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2.54707727671322</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8.521864217426122</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.5804147544943239</v>
-      </c>
-      <c r="K59" t="n">
-        <v>25.3474518214041</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-101229</v>
-      </c>
-      <c r="M59" t="n">
-        <v>-301.5190778303994</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-97820</v>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>11.08175357755092</v>
-      </c>
-      <c r="P59" t="n">
-        <v>15.92359362270073</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>14.86983549970351</v>
-      </c>
-      <c r="R59" t="n">
-        <v>23</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.0880835748601615</v>
-      </c>
-      <c r="T59" t="n">
-        <v>119.7748691099476</v>
-      </c>
-      <c r="U59" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="V59" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="W59" t="n">
-        <v>23.06</v>
       </c>
     </row>
   </sheetData>
